--- a/data/industry/CFM/RDIMM.xlsx
+++ b/data/industry/CFM/RDIMM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1C30EE-F3FA-4AF0-B8CE-1F0469B40FF7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B70725F-CDB5-479B-A6CD-938802CABCF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="610" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 RDIMM 16GB 3200" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="8">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -68,8 +68,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -132,26 +132,26 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
@@ -444,14 +444,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -709,11 +709,27 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>240</v>
+      </c>
+      <c r="F12" s="11">
+        <v>350</v>
+      </c>
+      <c r="G12" s="11">
+        <v>300</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
@@ -825,14 +841,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DCC6B8-7E19-4188-98AA-76DE911B494C}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1090,11 +1106,27 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>280</v>
+      </c>
+      <c r="F12" s="11">
+        <v>750</v>
+      </c>
+      <c r="G12" s="11">
+        <v>450</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
@@ -1206,15 +1238,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05E61F2-2635-4C27-8DCB-93976B9195D8}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="12"/>
     <col min="6" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1472,11 +1504,27 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>600</v>
+      </c>
+      <c r="F12" s="11">
+        <v>1300</v>
+      </c>
+      <c r="G12" s="11">
+        <v>800</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
@@ -1588,14 +1636,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBC2934-9EA8-4CA1-881F-5F7DC593D698}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1853,11 +1901,27 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>635</v>
+      </c>
+      <c r="F12" s="11">
+        <v>800</v>
+      </c>
+      <c r="G12" s="11">
+        <v>650</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
@@ -1969,15 +2033,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FF9896-5884-4059-8248-612FA72E9D05}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="12"/>
     <col min="6" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -2235,11 +2299,27 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>1200</v>
+      </c>
+      <c r="F12" s="11">
+        <v>2300</v>
+      </c>
+      <c r="G12" s="11">
+        <v>1220</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
@@ -2351,14 +2431,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1879A24C-F295-4F90-921D-1BCFB04E666C}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -2616,11 +2696,27 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="A12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46119</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>1950</v>
+      </c>
+      <c r="F12" s="11">
+        <v>4000</v>
+      </c>
+      <c r="G12" s="11">
+        <v>1980</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
